--- a/03_Cluster_groups/Proteome/02_Design_Contrasts/T2/c_data/design_contrasts.xlsx
+++ b/03_Cluster_groups/Proteome/02_Design_Contrasts/T2/c_data/design_contrasts.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="186">
   <si>
     <t>sheet</t>
   </si>
@@ -210,7 +210,7 @@
     <t>groups</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Proteome/01_Clustering/c_data/groups/T2.rds</t>
+    <t>02_Groups/Proteome/c_data/groups/T2.rds</t>
   </si>
   <si>
     <t>66d4ea9705e4ef793c273e79ff366700</t>
@@ -571,6 +571,12 @@
   </si>
   <si>
     <t>2.0.1</t>
+  </si>
+  <si>
+    <t>yaml</t>
+  </si>
+  <si>
+    <t>2.3.12</t>
   </si>
 </sst>
 </file>
@@ -1302,7 +1308,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -1965,6 +1971,17 @@
         <v>152</v>
       </c>
     </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>184</v>
+      </c>
+      <c r="B61" t="s">
+        <v>185</v>
+      </c>
+      <c r="C61" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
